--- a/schoolDocs/StudentImportData/Class7_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class7_ImportReady.xlsx
@@ -673,27 +673,27 @@
   <dimension ref="A1:U16"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="25.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="24.565" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="29.279" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="35.277" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="29.421" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="131.968" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.283" customWidth="true" style="0"/>
+    <col min="2" max="2" width="19.995" customWidth="true" style="0"/>
+    <col min="3" max="3" width="18.71" customWidth="true" style="0"/>
+    <col min="4" max="4" width="10.426" customWidth="true" style="0"/>
+    <col min="5" max="5" width="9.283" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11.569" customWidth="true" style="0"/>
+    <col min="7" max="7" width="25.708" customWidth="true" style="0"/>
+    <col min="8" max="8" width="17.567" customWidth="true" style="0"/>
+    <col min="9" max="9" width="15.139" customWidth="true" style="0"/>
+    <col min="10" max="10" width="24.565" customWidth="true" style="0"/>
+    <col min="11" max="11" width="29.279" customWidth="true" style="0"/>
+    <col min="12" max="12" width="35.277" customWidth="true" style="0"/>
+    <col min="13" max="13" width="12.854" customWidth="true" style="0"/>
+    <col min="14" max="14" width="26.993" customWidth="true" style="0"/>
+    <col min="15" max="15" width="16.282" customWidth="true" style="0"/>
+    <col min="16" max="16" width="29.421" customWidth="true" style="0"/>
+    <col min="17" max="17" width="16.282" customWidth="true" style="0"/>
+    <col min="18" max="18" width="23.423" customWidth="true" style="0"/>
+    <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
+    <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
+    <col min="21" max="21" width="131.968" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -786,7 +786,10 @@
       <c r="I2">
         <v>25</v>
       </c>
-      <c r="K2" s="5"/>
+      <c r="J2"/>
+      <c r="K2" s="5">
+        <v>12150</v>
+      </c>
       <c r="L2" t="s">
         <v>26</v>
       </c>
@@ -828,6 +831,8 @@
       <c r="H3" t="s">
         <v>33</v>
       </c>
+      <c r="I3"/>
+      <c r="J3"/>
       <c r="K3">
         <v>16200</v>
       </c>
@@ -869,6 +874,11 @@
       <c r="H4" t="s">
         <v>33</v>
       </c>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4">
+        <v>0</v>
+      </c>
       <c r="L4" t="s">
         <v>39</v>
       </c>
@@ -907,8 +917,10 @@
       <c r="H5" t="s">
         <v>33</v>
       </c>
+      <c r="I5"/>
+      <c r="J5"/>
       <c r="K5" s="5">
-        <v>12200</v>
+        <v>16200</v>
       </c>
       <c r="L5" t="s">
         <v>42</v>
@@ -951,6 +963,8 @@
       <c r="H6" t="s">
         <v>33</v>
       </c>
+      <c r="I6"/>
+      <c r="J6"/>
       <c r="K6">
         <v>16200</v>
       </c>
@@ -989,6 +1003,8 @@
       <c r="H7" t="s">
         <v>49</v>
       </c>
+      <c r="I7"/>
+      <c r="J7"/>
       <c r="K7">
         <v>16200</v>
       </c>
@@ -1024,6 +1040,8 @@
       <c r="H8" t="s">
         <v>49</v>
       </c>
+      <c r="I8"/>
+      <c r="J8"/>
       <c r="K8">
         <v>16200</v>
       </c>
@@ -1059,6 +1077,8 @@
       <c r="H9" t="s">
         <v>49</v>
       </c>
+      <c r="I9"/>
+      <c r="J9"/>
       <c r="K9">
         <v>16200</v>
       </c>
@@ -1094,6 +1114,8 @@
       <c r="H10" t="s">
         <v>49</v>
       </c>
+      <c r="I10"/>
+      <c r="J10"/>
       <c r="K10">
         <v>16200</v>
       </c>
@@ -1132,8 +1154,10 @@
       <c r="H11" t="s">
         <v>33</v>
       </c>
+      <c r="I11"/>
+      <c r="J11"/>
       <c r="K11">
-        <v>12000</v>
+        <v>12200</v>
       </c>
       <c r="L11" t="s">
         <v>61</v>
@@ -1176,6 +1200,11 @@
       <c r="H12" t="s">
         <v>66</v>
       </c>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12">
+        <v>0</v>
+      </c>
       <c r="L12" t="s">
         <v>67</v>
       </c>
@@ -1217,6 +1246,11 @@
       <c r="H13" t="s">
         <v>66</v>
       </c>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13">
+        <v>0</v>
+      </c>
       <c r="L13" t="s">
         <v>72</v>
       </c>
@@ -1258,6 +1292,8 @@
       <c r="H14" t="s">
         <v>33</v>
       </c>
+      <c r="I14"/>
+      <c r="J14"/>
       <c r="K14">
         <v>6000</v>
       </c>
@@ -1299,6 +1335,11 @@
       <c r="H15" t="s">
         <v>66</v>
       </c>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15">
+        <v>0</v>
+      </c>
       <c r="L15" t="s">
         <v>81</v>
       </c>
@@ -1339,6 +1380,11 @@
       </c>
       <c r="H16" t="s">
         <v>66</v>
+      </c>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16">
+        <v>0</v>
       </c>
       <c r="L16" t="s">
         <v>84</v>

--- a/schoolDocs/StudentImportData/Class7_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class7_ImportReady.xlsx
@@ -14,8 +14,34 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="U1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Calibri"/>
+            <b val="false"/>
+            <i val="false"/>
+            <strike val="false"/>
+            <color rgb="FF000000"/>
+            <sz val="11"/>
+            <u val="none"/>
+          </rPr>
+          <t xml:space="preserve">Only for RTE students. Alphanumeric, e.g. 26MS011157 (Year+StateCode+Sequence). Leave blank for non-RTE.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="85">
   <si>
     <t>Sr No</t>
   </si>
@@ -77,7 +103,7 @@
     <t>DGA Admission No</t>
   </si>
   <si>
-    <t>Notes for Verification (ignored on import)</t>
+    <t>RTE Application No</t>
   </si>
   <si>
     <t>Neel Ubale</t>
@@ -110,9 +136,6 @@
     <t>Home maker</t>
   </si>
   <si>
-    <t>DGA total ₹12150 (= 25% off ₹16200) but G col blank — assumed 25% discount. Collected ₹0. Please verify.</t>
-  </si>
-  <si>
     <t>Rehan Khan</t>
   </si>
   <si>
@@ -149,9 +172,6 @@
     <t>Farming and hotel</t>
   </si>
   <si>
-    <t>DGA shows ₹12200 for this boy (girls rate). System will charge ₹16200 as general. Please verify fee is correct.</t>
-  </si>
-  <si>
     <t>Gurnoor Singh</t>
   </si>
   <si>
@@ -173,9 +193,6 @@
     <t>19km</t>
   </si>
   <si>
-    <t>CoC student — full ₹16200 collected</t>
-  </si>
-  <si>
     <t>Shubham Kamble</t>
   </si>
   <si>
@@ -209,9 +226,6 @@
     <t>Asha Worker</t>
   </si>
   <si>
-    <t>Near-full payment — ₹12000 of ₹12200 collected (₹200 remaining)</t>
-  </si>
-  <si>
     <t>Shrushti Gardade</t>
   </si>
   <si>
@@ -227,7 +241,7 @@
     <t>Parlour</t>
   </si>
   <si>
-    <t>RTE — fees paid by government</t>
+    <t>25MS000046</t>
   </si>
   <si>
     <t>Samruddhi Karhe</t>
@@ -239,6 +253,9 @@
     <t>Owns garage</t>
   </si>
   <si>
+    <t>25MS000047</t>
+  </si>
+  <si>
     <t>Praniti Dhudhal</t>
   </si>
   <si>
@@ -254,9 +271,6 @@
     <t>Tea Shop</t>
   </si>
   <si>
-    <t>Partial — ₹6000 of ₹12200 collected</t>
-  </si>
-  <si>
     <t>Ananya Jadhav</t>
   </si>
   <si>
@@ -266,6 +280,9 @@
     <t>Driver</t>
   </si>
   <si>
+    <t>25MS000048</t>
+  </si>
+  <si>
     <t>Sushma Dagade</t>
   </si>
   <si>
@@ -276,6 +293,9 @@
   </si>
   <si>
     <t>0.5km</t>
+  </si>
+  <si>
+    <t>25MS000049</t>
   </si>
 </sst>
 </file>
@@ -327,12 +347,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7B3F00"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -340,6 +354,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD5EAD0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E4057"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -361,16 +381,16 @@
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -693,7 +713,7 @@
     <col min="18" max="18" width="23.423" customWidth="true" style="0"/>
     <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
     <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
-    <col min="21" max="21" width="131.968" customWidth="true" style="0"/>
+    <col min="21" max="21" width="20" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -727,10 +747,10 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -757,7 +777,7 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -787,7 +807,7 @@
         <v>25</v>
       </c>
       <c r="J2"/>
-      <c r="K2" s="5">
+      <c r="K2" s="4">
         <v>12150</v>
       </c>
       <c r="L2" t="s">
@@ -805,16 +825,14 @@
       <c r="R2" t="s">
         <v>30</v>
       </c>
-      <c r="U2" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="U2" s="4"/>
     </row>
     <row r="3" spans="1:21">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -829,7 +847,7 @@
         <v>8485054355</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I3"/>
       <c r="J3"/>
@@ -837,27 +855,28 @@
         <v>16200</v>
       </c>
       <c r="L3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" t="s">
         <v>34</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>35</v>
       </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>36</v>
-      </c>
-      <c r="P3" t="s">
-        <v>37</v>
       </c>
       <c r="R3" t="s">
         <v>30</v>
       </c>
+      <c r="U3"/>
     </row>
     <row r="4" spans="1:21">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -872,7 +891,7 @@
         <v>8805776662</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I4"/>
       <c r="J4"/>
@@ -880,27 +899,28 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" t="s">
         <v>39</v>
-      </c>
-      <c r="M4" t="s">
-        <v>35</v>
-      </c>
-      <c r="N4" t="s">
-        <v>36</v>
-      </c>
-      <c r="P4" t="s">
-        <v>40</v>
       </c>
       <c r="R4" t="s">
         <v>30</v>
       </c>
+      <c r="U4"/>
     </row>
     <row r="5" spans="1:21">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -915,38 +935,36 @@
         <v>9665537788</v>
       </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
-      <c r="K5" s="5">
+      <c r="K5" s="4">
         <v>16200</v>
       </c>
       <c r="L5" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P5" t="s">
         <v>42</v>
-      </c>
-      <c r="M5" t="s">
-        <v>35</v>
-      </c>
-      <c r="N5" t="s">
-        <v>36</v>
-      </c>
-      <c r="P5" t="s">
-        <v>43</v>
       </c>
       <c r="R5" t="s">
         <v>30</v>
       </c>
-      <c r="U5" s="5" t="s">
-        <v>44</v>
-      </c>
+      <c r="U5" s="4"/>
     </row>
     <row r="6" spans="1:21">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -961,7 +979,7 @@
         <v>9021305787</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -969,7 +987,7 @@
         <v>16200</v>
       </c>
       <c r="L6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M6" t="s">
         <v>27</v>
@@ -978,18 +996,19 @@
         <v>28</v>
       </c>
       <c r="P6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="R6" t="s">
         <v>30</v>
       </c>
+      <c r="U6"/>
     </row>
     <row r="7" spans="1:21">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -1001,7 +1020,7 @@
         <v>24</v>
       </c>
       <c r="H7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1012,21 +1031,19 @@
         <v>26</v>
       </c>
       <c r="M7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N7" t="s">
-        <v>51</v>
-      </c>
-      <c r="U7" t="s">
-        <v>52</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="U7"/>
     </row>
     <row r="8" spans="1:21">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
@@ -1038,7 +1055,7 @@
         <v>24</v>
       </c>
       <c r="H8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -1046,24 +1063,22 @@
         <v>16200</v>
       </c>
       <c r="L8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N8" t="s">
-        <v>51</v>
-      </c>
-      <c r="U8" t="s">
-        <v>52</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="U8"/>
     </row>
     <row r="9" spans="1:21">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -1075,7 +1090,7 @@
         <v>24</v>
       </c>
       <c r="H9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1083,24 +1098,22 @@
         <v>16200</v>
       </c>
       <c r="L9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N9" t="s">
-        <v>51</v>
-      </c>
-      <c r="U9" t="s">
-        <v>52</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="U9"/>
     </row>
     <row r="10" spans="1:21">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
@@ -1112,7 +1125,7 @@
         <v>24</v>
       </c>
       <c r="H10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -1120,27 +1133,25 @@
         <v>16200</v>
       </c>
       <c r="L10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N10" t="s">
-        <v>51</v>
-      </c>
-      <c r="U10" t="s">
-        <v>52</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="U10"/>
     </row>
     <row r="11" spans="1:21">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>23</v>
@@ -1152,7 +1163,7 @@
         <v>9860025125</v>
       </c>
       <c r="H11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -1160,7 +1171,7 @@
         <v>12200</v>
       </c>
       <c r="L11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="M11" t="s">
         <v>27</v>
@@ -1169,24 +1180,22 @@
         <v>28</v>
       </c>
       <c r="P11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="R11" t="s">
-        <v>63</v>
-      </c>
-      <c r="U11" t="s">
-        <v>64</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="U11"/>
     </row>
     <row r="12" spans="1:21">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
         <v>23</v>
@@ -1198,7 +1207,7 @@
         <v>9503293032</v>
       </c>
       <c r="H12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -1206,22 +1215,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="M12" t="s">
+        <v>34</v>
+      </c>
+      <c r="N12" t="s">
         <v>35</v>
       </c>
-      <c r="N12" t="s">
-        <v>36</v>
-      </c>
       <c r="P12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="R12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="U12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -1229,10 +1238,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
@@ -1244,7 +1253,7 @@
         <v>9075399050</v>
       </c>
       <c r="H13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -1252,16 +1261,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="M13" t="s">
+        <v>34</v>
+      </c>
+      <c r="N13" t="s">
         <v>35</v>
       </c>
-      <c r="N13" t="s">
-        <v>36</v>
-      </c>
       <c r="P13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="R13" t="s">
         <v>30</v>
@@ -1275,10 +1284,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
@@ -1290,7 +1299,7 @@
         <v>9730253332</v>
       </c>
       <c r="H14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -1298,33 +1307,31 @@
         <v>6000</v>
       </c>
       <c r="L14" t="s">
+        <v>72</v>
+      </c>
+      <c r="M14" t="s">
+        <v>73</v>
+      </c>
+      <c r="N14" t="s">
+        <v>74</v>
+      </c>
+      <c r="P14" t="s">
         <v>75</v>
-      </c>
-      <c r="M14" t="s">
-        <v>76</v>
-      </c>
-      <c r="N14" t="s">
-        <v>77</v>
-      </c>
-      <c r="P14" t="s">
-        <v>78</v>
       </c>
       <c r="R14" t="s">
         <v>30</v>
       </c>
-      <c r="U14" t="s">
-        <v>79</v>
-      </c>
+      <c r="U14"/>
     </row>
     <row r="15" spans="1:21">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
@@ -1333,7 +1340,7 @@
         <v>24</v>
       </c>
       <c r="H15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -1341,22 +1348,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="M15" t="s">
+        <v>34</v>
+      </c>
+      <c r="N15" t="s">
         <v>35</v>
       </c>
-      <c r="N15" t="s">
-        <v>36</v>
-      </c>
       <c r="P15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="R15" t="s">
         <v>30</v>
       </c>
       <c r="U15" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -1364,10 +1371,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
@@ -1379,7 +1386,7 @@
         <v>7558341731</v>
       </c>
       <c r="H16" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -1387,16 +1394,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="s">
+        <v>81</v>
+      </c>
+      <c r="M16" t="s">
+        <v>82</v>
+      </c>
+      <c r="N16" t="s">
+        <v>83</v>
+      </c>
+      <c r="U16" t="s">
         <v>84</v>
-      </c>
-      <c r="M16" t="s">
-        <v>85</v>
-      </c>
-      <c r="N16" t="s">
-        <v>86</v>
-      </c>
-      <c r="U16" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1411,6 +1418,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId_comments_vml1"/>
   <tableParts count="0"/>
 </worksheet>
 </file>
--- a/schoolDocs/StudentImportData/Class7_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class7_ImportReady.xlsx
@@ -825,6 +825,9 @@
       <c r="R2" t="s">
         <v>30</v>
       </c>
+      <c r="S2">
+        <v>27000010130</v>
+      </c>
       <c r="U2" s="4"/>
     </row>
     <row r="3" spans="1:21">
@@ -869,6 +872,9 @@
       <c r="R3" t="s">
         <v>30</v>
       </c>
+      <c r="S3">
+        <v>27000010131</v>
+      </c>
       <c r="U3"/>
     </row>
     <row r="4" spans="1:21">
@@ -913,6 +919,9 @@
       <c r="R4" t="s">
         <v>30</v>
       </c>
+      <c r="S4">
+        <v>27000010132</v>
+      </c>
       <c r="U4"/>
     </row>
     <row r="5" spans="1:21">
@@ -957,6 +966,9 @@
       <c r="R5" t="s">
         <v>30</v>
       </c>
+      <c r="S5">
+        <v>27000010133</v>
+      </c>
       <c r="U5" s="4"/>
     </row>
     <row r="6" spans="1:21">
@@ -1001,6 +1013,9 @@
       <c r="R6" t="s">
         <v>30</v>
       </c>
+      <c r="S6">
+        <v>27000010134</v>
+      </c>
       <c r="U6"/>
     </row>
     <row r="7" spans="1:21">
@@ -1036,6 +1051,9 @@
       <c r="N7" t="s">
         <v>49</v>
       </c>
+      <c r="S7">
+        <v>27000010135</v>
+      </c>
       <c r="U7"/>
     </row>
     <row r="8" spans="1:21">
@@ -1071,6 +1089,9 @@
       <c r="N8" t="s">
         <v>49</v>
       </c>
+      <c r="S8">
+        <v>27000010136</v>
+      </c>
       <c r="U8"/>
     </row>
     <row r="9" spans="1:21">
@@ -1106,6 +1127,9 @@
       <c r="N9" t="s">
         <v>49</v>
       </c>
+      <c r="S9">
+        <v>27000010137</v>
+      </c>
       <c r="U9"/>
     </row>
     <row r="10" spans="1:21">
@@ -1141,6 +1165,9 @@
       <c r="N10" t="s">
         <v>49</v>
       </c>
+      <c r="S10">
+        <v>27000010138</v>
+      </c>
       <c r="U10"/>
     </row>
     <row r="11" spans="1:21">
@@ -1185,6 +1212,9 @@
       <c r="R11" t="s">
         <v>60</v>
       </c>
+      <c r="S11">
+        <v>27000010139</v>
+      </c>
       <c r="U11"/>
     </row>
     <row r="12" spans="1:21">
@@ -1229,6 +1259,9 @@
       <c r="R12" t="s">
         <v>65</v>
       </c>
+      <c r="S12">
+        <v>27000010140</v>
+      </c>
       <c r="U12" t="s">
         <v>66</v>
       </c>
@@ -1275,6 +1308,9 @@
       <c r="R13" t="s">
         <v>30</v>
       </c>
+      <c r="S13">
+        <v>27000010141</v>
+      </c>
       <c r="U13" t="s">
         <v>70</v>
       </c>
@@ -1321,6 +1357,9 @@
       <c r="R14" t="s">
         <v>30</v>
       </c>
+      <c r="S14">
+        <v>27000010142</v>
+      </c>
       <c r="U14"/>
     </row>
     <row r="15" spans="1:21">
@@ -1362,6 +1401,9 @@
       <c r="R15" t="s">
         <v>30</v>
       </c>
+      <c r="S15">
+        <v>27000010143</v>
+      </c>
       <c r="U15" t="s">
         <v>79</v>
       </c>
@@ -1401,6 +1443,9 @@
       </c>
       <c r="N16" t="s">
         <v>83</v>
+      </c>
+      <c r="S16">
+        <v>27000010144</v>
       </c>
       <c r="U16" t="s">
         <v>84</v>
